--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19080" windowHeight="11920"/>
+    <workbookView windowWidth="19440" windowHeight="11920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>order</t>
   </si>
@@ -49,13 +49,16 @@
     <t>link</t>
   </si>
   <si>
-    <t>你的文字标题</t>
+    <t>示例数据</t>
   </si>
   <si>
-    <t>你的接口</t>
+    <t>2025-2026赛季 中国人寿 ·NYBO青少年篮球公开赛 上海徐汇赛区</t>
   </si>
   <si>
-    <t>你的网址</t>
+    <t>图片链接，cdn地址，必须是可以直接打开图片的地址</t>
+  </si>
+  <si>
+    <t>用于生成二维码的网站网址</t>
   </si>
 </sst>
 </file>
@@ -1034,20 +1037,20 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
-        <v>2947</v>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2">
-        <v>46004.375</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>8</v>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1055,107 +1058,52 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>2948</v>
+        <v>3011</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2">
-        <v>46005.375</v>
+        <v>46047.375</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
-        <v>2950</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2">
-        <v>46004.5833333333</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
-        <v>2951</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2">
-        <v>46005.3333333333</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
-        <v>2952</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2">
-        <v>46004.3333333333</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1">
-        <v>2954</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2">
-        <v>46005.5</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="1"/>
       <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6">
